--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -6191,8 +6191,8 @@
       <c r="D243" s="4">
         <v>138703</v>
       </c>
-      <c r="E243" s="2" t="s">
-        <v>10</v>
+      <c r="E243" s="2">
+        <v>2</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>7</v>
@@ -6204,6 +6204,24 @@
     <row r="244" spans="1:7">
       <c r="A244" s="2">
         <v>317</v>
+      </c>
+      <c r="B244" s="8">
+        <v>46219</v>
+      </c>
+      <c r="C244" s="8">
+        <v>46228</v>
+      </c>
+      <c r="D244" s="4">
+        <v>139947</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G244" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -11216,8 +11234,25 @@
       <c r="A205" s="2">
         <v>317</v>
       </c>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
+      <c r="B205" s="8">
+        <v>46219</v>
+      </c>
+      <c r="C205" s="8">
+        <v>46228</v>
+      </c>
+      <c r="D205" s="3">
+        <v>67725</v>
+      </c>
+      <c r="E205" s="6">
+        <f>D205/B服!D244</f>
+        <v>0.4839332032841</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" s="2">

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -6214,8 +6214,8 @@
       <c r="D244" s="4">
         <v>139947</v>
       </c>
-      <c r="E244" s="2" t="s">
-        <v>10</v>
+      <c r="E244" s="2">
+        <v>3</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>6</v>
@@ -6227,6 +6227,24 @@
     <row r="245" spans="1:7">
       <c r="A245" s="2">
         <v>318</v>
+      </c>
+      <c r="B245" s="8">
+        <v>46230</v>
+      </c>
+      <c r="C245" s="8">
+        <v>46239</v>
+      </c>
+      <c r="D245" s="4">
+        <v>132102</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G245" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -11258,8 +11276,25 @@
       <c r="A206" s="2">
         <v>318</v>
       </c>
-      <c r="F206" s="2"/>
-      <c r="G206" s="2"/>
+      <c r="B206" s="8">
+        <v>46230</v>
+      </c>
+      <c r="C206" s="8">
+        <v>46239</v>
+      </c>
+      <c r="D206" s="3">
+        <v>65536</v>
+      </c>
+      <c r="E206" s="6">
+        <f>D206/B服!D245</f>
+        <v>0.496101497327822</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" s="2">

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -6266,8 +6266,8 @@
       <c r="D246" s="4">
         <v>120251</v>
       </c>
-      <c r="E246" s="5" t="s">
-        <v>10</v>
+      <c r="E246" s="5">
+        <v>4</v>
       </c>
       <c r="F246" s="5" t="s">
         <v>7</v>
@@ -6279,6 +6279,24 @@
     <row r="247" spans="1:7">
       <c r="A247" s="5">
         <v>320</v>
+      </c>
+      <c r="B247" s="2">
+        <v>46251</v>
+      </c>
+      <c r="C247" s="2">
+        <v>46258</v>
+      </c>
+      <c r="D247" s="4">
+        <v>104962</v>
+      </c>
+      <c r="E247" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G247" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -11348,8 +11366,25 @@
       <c r="A208" s="5">
         <v>320</v>
       </c>
-      <c r="F208" s="5"/>
-      <c r="G208" s="5"/>
+      <c r="B208" s="2">
+        <v>46251</v>
+      </c>
+      <c r="C208" s="2">
+        <v>46258</v>
+      </c>
+      <c r="D208" s="3">
+        <v>50934</v>
+      </c>
+      <c r="E208" s="7">
+        <f>D208/B服!D247</f>
+        <v>0.485261332672777</v>
+      </c>
+      <c r="F208" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G208" s="5" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" s="5">

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="B服" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -6289,8 +6289,8 @@
       <c r="D247" s="4">
         <v>104962</v>
       </c>
-      <c r="E247" s="5" t="s">
-        <v>10</v>
+      <c r="E247" s="5">
+        <v>2</v>
       </c>
       <c r="F247" s="5" t="s">
         <v>8</v>
@@ -6302,6 +6302,24 @@
     <row r="248" spans="1:7">
       <c r="A248" s="5">
         <v>321</v>
+      </c>
+      <c r="B248" s="2">
+        <v>46260</v>
+      </c>
+      <c r="C248" s="2">
+        <v>46267</v>
+      </c>
+      <c r="D248" s="4">
+        <v>104559</v>
+      </c>
+      <c r="E248" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F248" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G248" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -11390,8 +11408,25 @@
       <c r="A209" s="5">
         <v>321</v>
       </c>
-      <c r="F209" s="5"/>
-      <c r="G209" s="5"/>
+      <c r="B209" s="2">
+        <v>46260</v>
+      </c>
+      <c r="C209" s="2">
+        <v>46267</v>
+      </c>
+      <c r="D209" s="3">
+        <v>40736</v>
+      </c>
+      <c r="E209" s="7">
+        <f>D209/B服!D248</f>
+        <v>0.389598217274457</v>
+      </c>
+      <c r="F209" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G209" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" s="5">

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -6326,6 +6326,24 @@
       <c r="A249" s="5">
         <v>322</v>
       </c>
+      <c r="B249" s="2">
+        <v>46269</v>
+      </c>
+      <c r="C249" s="2">
+        <v>46277</v>
+      </c>
+      <c r="D249" s="4">
+        <v>98408</v>
+      </c>
+      <c r="E249" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F249" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G249" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="250" spans="1:7">
       <c r="A250" s="5">
@@ -11432,8 +11450,25 @@
       <c r="A210" s="5">
         <v>322</v>
       </c>
-      <c r="F210" s="5"/>
-      <c r="G210" s="5"/>
+      <c r="B210" s="2">
+        <v>46269</v>
+      </c>
+      <c r="C210" s="2">
+        <v>46277</v>
+      </c>
+      <c r="D210" s="3">
+        <v>38554</v>
+      </c>
+      <c r="E210" s="7">
+        <f>D210/B服!D249</f>
+        <v>0.391777091293391</v>
+      </c>
+      <c r="F210" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G210" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="211" spans="1:7">
       <c r="A211" s="5">

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -6335,8 +6335,8 @@
       <c r="D249" s="4">
         <v>98408</v>
       </c>
-      <c r="E249" s="5" t="s">
-        <v>10</v>
+      <c r="E249" s="5">
+        <v>6</v>
       </c>
       <c r="F249" s="5" t="s">
         <v>7</v>
@@ -6348,6 +6348,24 @@
     <row r="250" spans="1:7">
       <c r="A250" s="5">
         <v>323</v>
+      </c>
+      <c r="B250" s="2">
+        <v>46279</v>
+      </c>
+      <c r="C250" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D250" s="4">
+        <v>42230</v>
+      </c>
+      <c r="E250" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F250" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G250" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -11474,8 +11492,25 @@
       <c r="A211" s="5">
         <v>323</v>
       </c>
-      <c r="F211" s="5"/>
-      <c r="G211" s="5"/>
+      <c r="B211" s="2">
+        <v>46279</v>
+      </c>
+      <c r="C211" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D211" s="3">
+        <v>8356</v>
+      </c>
+      <c r="E211" s="7">
+        <f>D211/B服!D250</f>
+        <v>0.197868813639593</v>
+      </c>
+      <c r="F211" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G211" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="212" spans="1:7">
       <c r="A212" s="5">

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -6358,8 +6358,8 @@
       <c r="D250" s="4">
         <v>42230</v>
       </c>
-      <c r="E250" s="5" t="s">
-        <v>10</v>
+      <c r="E250" s="5">
+        <v>4</v>
       </c>
       <c r="F250" s="5" t="s">
         <v>12</v>
@@ -6371,6 +6371,24 @@
     <row r="251" spans="1:7">
       <c r="A251" s="5">
         <v>324</v>
+      </c>
+      <c r="B251" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C251" s="2">
+        <v>46292</v>
+      </c>
+      <c r="D251" s="4">
+        <v>96188</v>
+      </c>
+      <c r="E251" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G251" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -11516,8 +11534,25 @@
       <c r="A212" s="5">
         <v>324</v>
       </c>
-      <c r="F212" s="5"/>
-      <c r="G212" s="5"/>
+      <c r="B212" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C212" s="2">
+        <v>46292</v>
+      </c>
+      <c r="D212" s="3">
+        <v>37877</v>
+      </c>
+      <c r="E212" s="7">
+        <f>D212/B服!D251</f>
+        <v>0.393780929014014</v>
+      </c>
+      <c r="F212" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G212" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" s="5">

--- a/backend/config/playernumber.xlsx
+++ b/backend/config/playernumber.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="B服" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -6381,8 +6381,8 @@
       <c r="D251" s="4">
         <v>96188</v>
       </c>
-      <c r="E251" s="5" t="s">
-        <v>10</v>
+      <c r="E251" s="5">
+        <v>4</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>11</v>
@@ -6394,6 +6394,24 @@
     <row r="252" spans="1:7">
       <c r="A252" s="5">
         <v>325</v>
+      </c>
+      <c r="B252" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C252" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D252" s="4">
+        <v>136279</v>
+      </c>
+      <c r="E252" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F252" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G252" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -11558,8 +11576,25 @@
       <c r="A213" s="5">
         <v>325</v>
       </c>
-      <c r="F213" s="5"/>
-      <c r="G213" s="5"/>
+      <c r="B213" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C213" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D213" s="3">
+        <v>65023</v>
+      </c>
+      <c r="E213" s="7">
+        <f>D213/B服!D252</f>
+        <v>0.477131472934201</v>
+      </c>
+      <c r="F213" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G213" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" s="5">
